--- a/Documents/タスク編集設計書 .xlsx
+++ b/Documents/タスク編集設計書 .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-24\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6902E74-FD13-44C6-AA82-95324A94C380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA552AFD-E5AE-475E-BA12-776828C08CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,18 @@
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
     <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
+    <sheet name="JUnitテスト仕様書兼報告書 (2)" sheetId="10" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="範囲１" localSheetId="6">#REF!</definedName>
+    <definedName name="範囲１">#REF!</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="128">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -762,6 +766,142 @@
     <t>画面遷移図</t>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>JUnitテスト仕様書兼報告書</t>
+    <rPh sb="8" eb="11">
+      <t>シヨウショ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ホウコクショ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>システム名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>会社名</t>
+    <rPh sb="0" eb="3">
+      <t>カイシャメイ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>コンサイズ</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+    <rPh sb="6" eb="7">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>タスク一覧</t>
+    <rPh sb="3" eb="5">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>作成日</t>
+    <rPh sb="0" eb="3">
+      <t>サクセイビ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>実施者</t>
+    <rPh sb="0" eb="2">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シャ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>分類</t>
+    <rPh sb="0" eb="2">
+      <t>ブンルイ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>テストクラス</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>検証するメソッド</t>
+    <rPh sb="0" eb="2">
+      <t>ケンショウ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>期待する結果</t>
+    <rPh sb="0" eb="2">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>実施日</t>
+    <rPh sb="0" eb="3">
+      <t>ジッシビ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>備考・特記事項</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トッキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>正常系</t>
+    <rPh sb="0" eb="3">
+      <t>セイジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>TaskDAOTest</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>update()</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>count==1</t>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -770,7 +910,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -854,8 +994,46 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -868,8 +1046,14 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="57">
+  <borders count="71">
     <border>
       <left/>
       <right/>
@@ -1529,13 +1713,193 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1680,6 +2044,45 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="57" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="62" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="16" fillId="0" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="67" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1968,9 +2371,21 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1980,23 +2395,106 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="67" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="68" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="59" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="65" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="66" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="58" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="60" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="5">
     <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{6C10B5B7-E36B-40F5-9E99-A4A9558B5B5A}"/>
+    <cellStyle name="標準_生産計画ED書" xfId="3" xr:uid="{4DFE3633-1B59-43CE-8502-06E7AFD138DD}"/>
+    <cellStyle name="標準_東京理科大DBレイアウト" xfId="4" xr:uid="{ECCD0612-EF6C-4CEE-A273-74138412619D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2895,85 +3393,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2993,46 +3491,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="55" t="s">
+      <c r="E8" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="52"/>
-      <c r="M8" s="52"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="65"/>
+      <c r="L8" s="65"/>
+      <c r="M8" s="65"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="48" t="s">
+      <c r="G13" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="50"/>
-      <c r="I13" s="48" t="s">
+      <c r="H13" s="63"/>
+      <c r="I13" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="49"/>
-      <c r="K13" s="50"/>
+      <c r="J13" s="62"/>
+      <c r="K13" s="63"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="48"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="50"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="63"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="48"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="50"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="63"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3041,13 +3539,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="51" t="s">
+      <c r="G17" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
+      <c r="H17" s="65"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="65"/>
+      <c r="K17" s="65"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4062,19 +4560,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="81" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="64"/>
-      <c r="F1" s="81" t="s">
+      <c r="E1" s="77"/>
+      <c r="F1" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="64"/>
+      <c r="G1" s="77"/>
       <c r="H1" s="38" t="s">
         <v>7</v>
       </c>
@@ -4086,190 +4584,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="75"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="82" t="s">
+      <c r="A2" s="88"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="83"/>
-      <c r="F2" s="82" t="s">
+      <c r="E2" s="96"/>
+      <c r="F2" s="95" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="83"/>
-      <c r="H2" s="86">
+      <c r="G2" s="96"/>
+      <c r="H2" s="99">
         <v>45806</v>
       </c>
-      <c r="I2" s="56" t="s">
+      <c r="I2" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="59"/>
+      <c r="J2" s="72"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="75"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="60"/>
+      <c r="A3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="78"/>
-      <c r="B4" s="79"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="61"/>
+      <c r="A4" s="91"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="74"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="63"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="65" t="s">
+      <c r="B5" s="76"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="66"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="79"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="80" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="68"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="70" t="s">
+      <c r="B6" s="81"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="83" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="71"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="84"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="68"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="70" t="s">
+      <c r="B7" s="81"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="71"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="84"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="68"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="70" t="s">
+      <c r="B8" s="81"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="71"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="84"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="92" t="s">
+      <c r="A9" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="95" t="s">
+      <c r="B9" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="96" t="s">
+      <c r="C9" s="82"/>
+      <c r="D9" s="109" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="71"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+      <c r="J9" s="84"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="93"/>
-      <c r="B10" s="95" t="s">
+      <c r="A10" s="106"/>
+      <c r="B10" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="69"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="68"/>
-      <c r="J10" s="71"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="84"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="94"/>
-      <c r="B11" s="95" t="s">
+      <c r="A11" s="107"/>
+      <c r="B11" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="69"/>
-      <c r="D11" s="96" t="s">
+      <c r="C11" s="82"/>
+      <c r="D11" s="109" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="68"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="68"/>
-      <c r="I11" s="68"/>
-      <c r="J11" s="71"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="84"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="68"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="70" t="s">
+      <c r="B12" s="81"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="68"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="68"/>
-      <c r="H12" s="68"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="71"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="84"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="87" t="s">
+      <c r="A13" s="100" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="88"/>
-      <c r="C13" s="89"/>
-      <c r="D13" s="90"/>
-      <c r="E13" s="88"/>
-      <c r="F13" s="88"/>
-      <c r="G13" s="88"/>
-      <c r="H13" s="88"/>
-      <c r="I13" s="88"/>
-      <c r="J13" s="91"/>
+      <c r="B13" s="101"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="101"/>
+      <c r="F13" s="101"/>
+      <c r="G13" s="101"/>
+      <c r="H13" s="101"/>
+      <c r="I13" s="101"/>
+      <c r="J13" s="104"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5306,19 +5804,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="110" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="81" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="64"/>
-      <c r="F1" s="81" t="s">
+      <c r="E1" s="77"/>
+      <c r="F1" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="64"/>
+      <c r="G1" s="77"/>
       <c r="H1" s="37" t="s">
         <v>7</v>
       </c>
@@ -5330,46 +5828,46 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="75"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="82" t="s">
+      <c r="A2" s="88"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="83"/>
-      <c r="F2" s="82" t="s">
+      <c r="E2" s="96"/>
+      <c r="F2" s="95" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="83"/>
-      <c r="H2" s="86">
+      <c r="G2" s="96"/>
+      <c r="H2" s="99">
         <v>45806</v>
       </c>
-      <c r="I2" s="56"/>
-      <c r="J2" s="59"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="72"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="75"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="60"/>
+      <c r="A3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="78"/>
-      <c r="B4" s="79"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="61"/>
+      <c r="A4" s="91"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="74"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="42"/>
@@ -6726,19 +7224,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="118" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="113" t="s">
+      <c r="B1" s="119"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="126" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="114"/>
-      <c r="F1" s="113" t="s">
+      <c r="E1" s="127"/>
+      <c r="F1" s="126" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="114"/>
+      <c r="G1" s="127"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -6750,48 +7248,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="108"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="115" t="s">
+      <c r="A2" s="121"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="128" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="116"/>
-      <c r="F2" s="115" t="s">
+      <c r="E2" s="129"/>
+      <c r="F2" s="128" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="116"/>
-      <c r="H2" s="98">
+      <c r="G2" s="129"/>
+      <c r="H2" s="111">
         <v>45810</v>
       </c>
-      <c r="I2" s="101" t="s">
+      <c r="I2" s="114" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="102"/>
+      <c r="J2" s="115"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="108"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="103"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="130"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="112"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="116"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="110"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="104"/>
+      <c r="A4" s="123"/>
+      <c r="B4" s="124"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="131"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="117"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -8142,19 +8640,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="118" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="113" t="s">
+      <c r="B1" s="119"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="126" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="114"/>
-      <c r="F1" s="113" t="s">
+      <c r="E1" s="127"/>
+      <c r="F1" s="126" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="114"/>
+      <c r="G1" s="127"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -8166,190 +8664,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="108"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="115" t="s">
+      <c r="A2" s="121"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="128" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="116"/>
-      <c r="F2" s="115">
+      <c r="E2" s="129"/>
+      <c r="F2" s="128">
         <v>56</v>
       </c>
-      <c r="G2" s="116"/>
-      <c r="H2" s="98">
+      <c r="G2" s="129"/>
+      <c r="H2" s="111">
         <v>45810</v>
       </c>
-      <c r="I2" s="101" t="s">
+      <c r="I2" s="114" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="102"/>
+      <c r="J2" s="115"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="108"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="103"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="130"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="112"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="116"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="108"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="103"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="116"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="122" t="s">
+      <c r="A5" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="123"/>
-      <c r="C5" s="114"/>
-      <c r="D5" s="125" t="s">
+      <c r="B5" s="136"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="138" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="123"/>
-      <c r="F5" s="123"/>
-      <c r="G5" s="123"/>
-      <c r="H5" s="123"/>
-      <c r="I5" s="123"/>
-      <c r="J5" s="126"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
+      <c r="G5" s="136"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="139"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="124" t="s">
+      <c r="A6" s="137" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="120"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="133"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="127"/>
-      <c r="B7" s="128"/>
-      <c r="C7" s="128"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="128"/>
-      <c r="G7" s="128"/>
-      <c r="H7" s="128"/>
-      <c r="I7" s="128"/>
-      <c r="J7" s="129"/>
+      <c r="A7" s="140"/>
+      <c r="B7" s="141"/>
+      <c r="C7" s="141"/>
+      <c r="D7" s="141"/>
+      <c r="E7" s="141"/>
+      <c r="F7" s="141"/>
+      <c r="G7" s="141"/>
+      <c r="H7" s="141"/>
+      <c r="I7" s="141"/>
+      <c r="J7" s="142"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="108"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="130"/>
+      <c r="A8" s="121"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="143"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="108"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="130"/>
+      <c r="A9" s="121"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="143"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="108"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="130"/>
+      <c r="A10" s="121"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="143"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="108"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="130"/>
+      <c r="A11" s="121"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="143"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="108"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="130"/>
+      <c r="A12" s="121"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="143"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="108"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="130"/>
+      <c r="A13" s="121"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="143"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="124" t="s">
+      <c r="A14" s="137" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="120"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="133"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="124" t="s">
+      <c r="A15" s="137" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="49"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="119" t="s">
+      <c r="B15" s="62"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="132" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="50"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="63"/>
       <c r="I15" s="14" t="s">
         <v>26</v>
       </c>
@@ -8358,11 +8856,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="49"/>
-      <c r="C16" s="50"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="63"/>
       <c r="D16" s="14" t="s">
         <v>28</v>
       </c>
@@ -8375,18 +8873,18 @@
       <c r="G16" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="131" t="s">
+      <c r="H16" s="144" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="49"/>
-      <c r="J16" s="120"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="133"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="121">
+      <c r="A17" s="134">
         <v>1</v>
       </c>
-      <c r="B17" s="49"/>
-      <c r="C17" s="50"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="63"/>
       <c r="D17" s="16" t="s">
         <v>69</v>
       </c>
@@ -8399,16 +8897,16 @@
       <c r="G17" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H17" s="119"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="120"/>
+      <c r="H17" s="132"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="133"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="121">
+      <c r="A18" s="134">
         <v>2</v>
       </c>
-      <c r="B18" s="49"/>
-      <c r="C18" s="50"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="63"/>
       <c r="D18" s="16" t="s">
         <v>75</v>
       </c>
@@ -8421,16 +8919,16 @@
       <c r="G18" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H18" s="119"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="120"/>
+      <c r="H18" s="132"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="133"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="121">
+      <c r="A19" s="134">
         <v>3</v>
       </c>
-      <c r="B19" s="49"/>
-      <c r="C19" s="50"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="63"/>
       <c r="D19" s="16" t="s">
         <v>76</v>
       </c>
@@ -8443,16 +8941,16 @@
       <c r="G19" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H19" s="119"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="120"/>
+      <c r="H19" s="132"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="133"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="121">
+      <c r="A20" s="134">
         <v>4</v>
       </c>
-      <c r="B20" s="49"/>
-      <c r="C20" s="50"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="63"/>
       <c r="D20" s="16" t="s">
         <v>77</v>
       </c>
@@ -8465,16 +8963,16 @@
       <c r="G20" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="H20" s="119"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="120"/>
+      <c r="H20" s="132"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="133"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="121">
+      <c r="A21" s="134">
         <v>5</v>
       </c>
-      <c r="B21" s="49"/>
-      <c r="C21" s="50"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="63"/>
       <c r="D21" s="16" t="s">
         <v>78</v>
       </c>
@@ -8487,16 +8985,16 @@
       <c r="G21" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="H21" s="119"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="120"/>
+      <c r="H21" s="132"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="133"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="121">
+      <c r="A22" s="134">
         <v>6</v>
       </c>
-      <c r="B22" s="49"/>
-      <c r="C22" s="50"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="63"/>
       <c r="D22" s="16" t="s">
         <v>71</v>
       </c>
@@ -8509,16 +9007,16 @@
       <c r="G22" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="H22" s="119"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="120"/>
+      <c r="H22" s="132"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="133"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="121">
+      <c r="A23" s="134">
         <v>7</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="50"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="63"/>
       <c r="D23" s="18" t="s">
         <v>71</v>
       </c>
@@ -8531,9 +9029,9 @@
       <c r="G23" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="H23" s="132"/>
-      <c r="I23" s="133"/>
-      <c r="J23" s="134"/>
+      <c r="H23" s="145"/>
+      <c r="I23" s="146"/>
+      <c r="J23" s="147"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9564,190 +10062,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="163" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="113" t="s">
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="126" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="113" t="s">
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="126" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="123"/>
-      <c r="M1" s="123"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="113" t="s">
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="126" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="113" t="s">
+      <c r="P1" s="127"/>
+      <c r="Q1" s="126" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="114"/>
-      <c r="S1" s="113" t="s">
+      <c r="R1" s="127"/>
+      <c r="S1" s="126" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="126"/>
+      <c r="T1" s="139"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="108"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="115" t="s">
+      <c r="A2" s="121"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="128" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="115" t="s">
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="128" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="151">
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="161">
         <v>45821</v>
       </c>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="115" t="s">
+      <c r="P2" s="129"/>
+      <c r="Q2" s="128" t="s">
         <v>56</v>
       </c>
-      <c r="R2" s="116"/>
-      <c r="S2" s="115"/>
-      <c r="T2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="128"/>
+      <c r="T2" s="142"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="108"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="109"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="109"/>
-      <c r="O3" s="117"/>
-      <c r="P3" s="109"/>
-      <c r="Q3" s="117"/>
-      <c r="R3" s="109"/>
-      <c r="S3" s="117"/>
-      <c r="T3" s="130"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="130"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="122"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="122"/>
+      <c r="Q3" s="130"/>
+      <c r="R3" s="122"/>
+      <c r="S3" s="130"/>
+      <c r="T3" s="143"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="110"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="111"/>
-      <c r="M4" s="111"/>
-      <c r="N4" s="112"/>
-      <c r="O4" s="118"/>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="145"/>
+      <c r="A4" s="123"/>
+      <c r="B4" s="124"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="124"/>
+      <c r="N4" s="125"/>
+      <c r="O4" s="131"/>
+      <c r="P4" s="125"/>
+      <c r="Q4" s="131"/>
+      <c r="R4" s="125"/>
+      <c r="S4" s="131"/>
+      <c r="T4" s="162"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="122" t="s">
+      <c r="A5" s="135" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="123"/>
-      <c r="C5" s="123"/>
-      <c r="D5" s="123"/>
-      <c r="E5" s="123"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="142" t="s">
+      <c r="B5" s="136"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="127"/>
+      <c r="G5" s="155" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="123"/>
-      <c r="I5" s="123"/>
-      <c r="J5" s="123"/>
-      <c r="K5" s="123"/>
-      <c r="L5" s="123"/>
-      <c r="M5" s="123"/>
-      <c r="N5" s="123"/>
-      <c r="O5" s="123"/>
-      <c r="P5" s="123"/>
-      <c r="Q5" s="123"/>
-      <c r="R5" s="123"/>
-      <c r="S5" s="123"/>
-      <c r="T5" s="126"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="136"/>
+      <c r="K5" s="136"/>
+      <c r="L5" s="136"/>
+      <c r="M5" s="136"/>
+      <c r="N5" s="136"/>
+      <c r="O5" s="136"/>
+      <c r="P5" s="136"/>
+      <c r="Q5" s="136"/>
+      <c r="R5" s="136"/>
+      <c r="S5" s="136"/>
+      <c r="T5" s="139"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="124" t="s">
+      <c r="A6" s="137" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="119" t="s">
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="132" t="s">
         <v>107</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="49"/>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49"/>
-      <c r="T6" s="120"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="62"/>
+      <c r="T6" s="133"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="124" t="s">
+      <c r="A7" s="137" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="119" t="s">
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="132" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="49"/>
-      <c r="M7" s="49"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="49"/>
-      <c r="R7" s="49"/>
-      <c r="S7" s="49"/>
-      <c r="T7" s="120"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="62"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="62"/>
+      <c r="Q7" s="62"/>
+      <c r="R7" s="62"/>
+      <c r="S7" s="62"/>
+      <c r="T7" s="133"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -9946,37 +10444,37 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="124" t="s">
+      <c r="A15" s="137" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="144" t="s">
+      <c r="B15" s="63"/>
+      <c r="C15" s="160" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="50"/>
-      <c r="E15" s="131" t="s">
+      <c r="D15" s="63"/>
+      <c r="E15" s="144" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="50"/>
-      <c r="G15" s="131" t="s">
+      <c r="F15" s="63"/>
+      <c r="G15" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="49"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="131" t="s">
+      <c r="H15" s="62"/>
+      <c r="I15" s="63"/>
+      <c r="J15" s="144" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="50"/>
-      <c r="L15" s="131" t="s">
+      <c r="K15" s="63"/>
+      <c r="L15" s="144" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="49"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="131" t="s">
+      <c r="M15" s="62"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="144" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="50"/>
+      <c r="P15" s="62"/>
+      <c r="Q15" s="63"/>
       <c r="R15" s="14" t="s">
         <v>49</v>
       </c>
@@ -9988,37 +10486,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="135">
+      <c r="A16" s="148">
         <v>1</v>
       </c>
-      <c r="B16" s="50"/>
-      <c r="C16" s="136" t="s">
+      <c r="B16" s="63"/>
+      <c r="C16" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="50"/>
-      <c r="E16" s="136" t="s">
+      <c r="D16" s="63"/>
+      <c r="E16" s="149" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="50"/>
-      <c r="G16" s="143" t="s">
+      <c r="F16" s="63"/>
+      <c r="G16" s="156" t="s">
         <v>90</v>
       </c>
-      <c r="H16" s="49"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="143" t="s">
+      <c r="H16" s="62"/>
+      <c r="I16" s="63"/>
+      <c r="J16" s="156" t="s">
         <v>91</v>
       </c>
-      <c r="K16" s="50"/>
-      <c r="L16" s="150" t="s">
+      <c r="K16" s="63"/>
+      <c r="L16" s="157" t="s">
         <v>92</v>
       </c>
-      <c r="M16" s="148"/>
-      <c r="N16" s="149"/>
-      <c r="O16" s="140" t="s">
+      <c r="M16" s="158"/>
+      <c r="N16" s="159"/>
+      <c r="O16" s="153" t="s">
         <v>93</v>
       </c>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="50"/>
+      <c r="P16" s="62"/>
+      <c r="Q16" s="63"/>
       <c r="R16" s="32"/>
       <c r="S16" s="32"/>
       <c r="T16" s="33"/>
@@ -10030,37 +10528,37 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="62.25" customHeight="1">
-      <c r="A17" s="135">
+      <c r="A17" s="148">
         <v>2</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="136" t="s">
+      <c r="B17" s="63"/>
+      <c r="C17" s="149" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="50"/>
-      <c r="E17" s="136" t="s">
+      <c r="D17" s="63"/>
+      <c r="E17" s="149" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="50"/>
-      <c r="G17" s="143" t="s">
+      <c r="F17" s="63"/>
+      <c r="G17" s="156" t="s">
         <v>96</v>
       </c>
-      <c r="H17" s="49"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="143" t="s">
+      <c r="H17" s="62"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="156" t="s">
         <v>97</v>
       </c>
-      <c r="K17" s="50"/>
-      <c r="L17" s="140" t="s">
+      <c r="K17" s="63"/>
+      <c r="L17" s="153" t="s">
         <v>98</v>
       </c>
-      <c r="M17" s="49"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="140" t="s">
+      <c r="M17" s="62"/>
+      <c r="N17" s="63"/>
+      <c r="O17" s="153" t="s">
         <v>99</v>
       </c>
-      <c r="P17" s="49"/>
-      <c r="Q17" s="50"/>
+      <c r="P17" s="62"/>
+      <c r="Q17" s="63"/>
       <c r="R17" s="32"/>
       <c r="S17" s="32"/>
       <c r="T17" s="33"/>
@@ -10072,37 +10570,37 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="54" customHeight="1">
-      <c r="A18" s="135">
+      <c r="A18" s="148">
         <v>3</v>
       </c>
-      <c r="B18" s="50"/>
-      <c r="C18" s="136" t="s">
+      <c r="B18" s="63"/>
+      <c r="C18" s="149" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="50"/>
-      <c r="E18" s="136" t="s">
+      <c r="D18" s="63"/>
+      <c r="E18" s="149" t="s">
         <v>95</v>
       </c>
-      <c r="F18" s="50"/>
-      <c r="G18" s="143" t="s">
+      <c r="F18" s="63"/>
+      <c r="G18" s="156" t="s">
         <v>100</v>
       </c>
-      <c r="H18" s="49"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="143" t="s">
+      <c r="H18" s="62"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="K18" s="50"/>
-      <c r="L18" s="140" t="s">
+      <c r="K18" s="63"/>
+      <c r="L18" s="153" t="s">
         <v>102</v>
       </c>
-      <c r="M18" s="49"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="140" t="s">
+      <c r="M18" s="62"/>
+      <c r="N18" s="63"/>
+      <c r="O18" s="153" t="s">
         <v>103</v>
       </c>
-      <c r="P18" s="49"/>
-      <c r="Q18" s="50"/>
+      <c r="P18" s="62"/>
+      <c r="Q18" s="63"/>
       <c r="R18" s="32"/>
       <c r="S18" s="32"/>
       <c r="T18" s="33"/>
@@ -10114,37 +10612,37 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="69.75" customHeight="1">
-      <c r="A19" s="135">
+      <c r="A19" s="148">
         <v>4</v>
       </c>
-      <c r="B19" s="50"/>
-      <c r="C19" s="136" t="s">
+      <c r="B19" s="63"/>
+      <c r="C19" s="149" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="50"/>
-      <c r="E19" s="136" t="s">
+      <c r="D19" s="63"/>
+      <c r="E19" s="149" t="s">
         <v>95</v>
       </c>
-      <c r="F19" s="50"/>
-      <c r="G19" s="143" t="s">
+      <c r="F19" s="63"/>
+      <c r="G19" s="156" t="s">
         <v>104</v>
       </c>
-      <c r="H19" s="49"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="143" t="s">
+      <c r="H19" s="62"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="156" t="s">
         <v>105</v>
       </c>
-      <c r="K19" s="50"/>
-      <c r="L19" s="140" t="s">
+      <c r="K19" s="63"/>
+      <c r="L19" s="153" t="s">
         <v>102</v>
       </c>
-      <c r="M19" s="49"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="140" t="s">
+      <c r="M19" s="62"/>
+      <c r="N19" s="63"/>
+      <c r="O19" s="153" t="s">
         <v>106</v>
       </c>
-      <c r="P19" s="49"/>
-      <c r="Q19" s="50"/>
+      <c r="P19" s="62"/>
+      <c r="Q19" s="63"/>
       <c r="R19" s="32"/>
       <c r="S19" s="32"/>
       <c r="T19" s="33"/>
@@ -10156,23 +10654,23 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="57" customHeight="1">
-      <c r="A20" s="135"/>
-      <c r="B20" s="50"/>
-      <c r="C20" s="136"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="136"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="143"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="143"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="140"/>
-      <c r="M20" s="49"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="140"/>
-      <c r="P20" s="49"/>
-      <c r="Q20" s="50"/>
+      <c r="A20" s="148"/>
+      <c r="B20" s="63"/>
+      <c r="C20" s="149"/>
+      <c r="D20" s="63"/>
+      <c r="E20" s="149"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="156"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="156"/>
+      <c r="K20" s="63"/>
+      <c r="L20" s="153"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="63"/>
+      <c r="O20" s="153"/>
+      <c r="P20" s="62"/>
+      <c r="Q20" s="63"/>
       <c r="R20" s="32"/>
       <c r="S20" s="32"/>
       <c r="T20" s="33"/>
@@ -10184,23 +10682,23 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="135"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="136"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="136"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="143"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="140"/>
-      <c r="M21" s="49"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="140"/>
-      <c r="P21" s="49"/>
-      <c r="Q21" s="50"/>
+      <c r="A21" s="148"/>
+      <c r="B21" s="63"/>
+      <c r="C21" s="149"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="149"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="156"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="63"/>
+      <c r="J21" s="156"/>
+      <c r="K21" s="63"/>
+      <c r="L21" s="153"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="63"/>
+      <c r="O21" s="153"/>
+      <c r="P21" s="62"/>
+      <c r="Q21" s="63"/>
       <c r="R21" s="32"/>
       <c r="S21" s="32"/>
       <c r="T21" s="33"/>
@@ -10212,23 +10710,23 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="135"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="136"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="136"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="143"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="143"/>
-      <c r="K22" s="50"/>
-      <c r="L22" s="140"/>
-      <c r="M22" s="49"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="140"/>
-      <c r="P22" s="49"/>
-      <c r="Q22" s="50"/>
+      <c r="A22" s="148"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="149"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="149"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="156"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="156"/>
+      <c r="K22" s="63"/>
+      <c r="L22" s="153"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="63"/>
+      <c r="O22" s="153"/>
+      <c r="P22" s="62"/>
+      <c r="Q22" s="63"/>
       <c r="R22" s="32"/>
       <c r="S22" s="32"/>
       <c r="T22" s="33"/>
@@ -10240,23 +10738,23 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="135"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="136"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="136"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="143"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="50"/>
-      <c r="J23" s="143"/>
-      <c r="K23" s="50"/>
-      <c r="L23" s="140"/>
-      <c r="M23" s="49"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="140"/>
-      <c r="P23" s="49"/>
-      <c r="Q23" s="50"/>
+      <c r="A23" s="148"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="149"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="149"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="156"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="63"/>
+      <c r="J23" s="156"/>
+      <c r="K23" s="63"/>
+      <c r="L23" s="153"/>
+      <c r="M23" s="62"/>
+      <c r="N23" s="63"/>
+      <c r="O23" s="153"/>
+      <c r="P23" s="62"/>
+      <c r="Q23" s="63"/>
       <c r="R23" s="32"/>
       <c r="S23" s="32"/>
       <c r="T23" s="33"/>
@@ -10268,23 +10766,23 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="135"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="136"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="136"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="143"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="143"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="140"/>
-      <c r="M24" s="49"/>
-      <c r="N24" s="50"/>
-      <c r="O24" s="140"/>
-      <c r="P24" s="49"/>
-      <c r="Q24" s="50"/>
+      <c r="A24" s="148"/>
+      <c r="B24" s="63"/>
+      <c r="C24" s="149"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="149"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="156"/>
+      <c r="H24" s="62"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="156"/>
+      <c r="K24" s="63"/>
+      <c r="L24" s="153"/>
+      <c r="M24" s="62"/>
+      <c r="N24" s="63"/>
+      <c r="O24" s="153"/>
+      <c r="P24" s="62"/>
+      <c r="Q24" s="63"/>
       <c r="R24" s="32"/>
       <c r="S24" s="32"/>
       <c r="T24" s="33"/>
@@ -10296,23 +10794,23 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="135"/>
-      <c r="B25" s="50"/>
-      <c r="C25" s="136"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="136"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="143"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="143"/>
-      <c r="K25" s="50"/>
-      <c r="L25" s="140"/>
-      <c r="M25" s="49"/>
-      <c r="N25" s="50"/>
-      <c r="O25" s="140"/>
-      <c r="P25" s="49"/>
-      <c r="Q25" s="50"/>
+      <c r="A25" s="148"/>
+      <c r="B25" s="63"/>
+      <c r="C25" s="149"/>
+      <c r="D25" s="63"/>
+      <c r="E25" s="149"/>
+      <c r="F25" s="63"/>
+      <c r="G25" s="156"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="63"/>
+      <c r="J25" s="156"/>
+      <c r="K25" s="63"/>
+      <c r="L25" s="153"/>
+      <c r="M25" s="62"/>
+      <c r="N25" s="63"/>
+      <c r="O25" s="153"/>
+      <c r="P25" s="62"/>
+      <c r="Q25" s="63"/>
       <c r="R25" s="32"/>
       <c r="S25" s="32"/>
       <c r="T25" s="33"/>
@@ -10324,23 +10822,23 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="135"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="136"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="136"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="143"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="143"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="140"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="140"/>
-      <c r="P26" s="49"/>
-      <c r="Q26" s="50"/>
+      <c r="A26" s="148"/>
+      <c r="B26" s="63"/>
+      <c r="C26" s="149"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="149"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="156"/>
+      <c r="H26" s="62"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="156"/>
+      <c r="K26" s="63"/>
+      <c r="L26" s="153"/>
+      <c r="M26" s="62"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="153"/>
+      <c r="P26" s="62"/>
+      <c r="Q26" s="63"/>
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
       <c r="T26" s="33"/>
@@ -10352,23 +10850,23 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="135"/>
-      <c r="B27" s="50"/>
-      <c r="C27" s="136"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="136"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="143"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="143"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="140"/>
-      <c r="M27" s="49"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="140"/>
-      <c r="P27" s="49"/>
-      <c r="Q27" s="50"/>
+      <c r="A27" s="148"/>
+      <c r="B27" s="63"/>
+      <c r="C27" s="149"/>
+      <c r="D27" s="63"/>
+      <c r="E27" s="149"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="156"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="63"/>
+      <c r="J27" s="156"/>
+      <c r="K27" s="63"/>
+      <c r="L27" s="153"/>
+      <c r="M27" s="62"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="153"/>
+      <c r="P27" s="62"/>
+      <c r="Q27" s="63"/>
       <c r="R27" s="32"/>
       <c r="S27" s="32"/>
       <c r="T27" s="33"/>
@@ -10380,23 +10878,23 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="135"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="136"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="136"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="143"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="143"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="140"/>
-      <c r="M28" s="49"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="140"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="50"/>
+      <c r="A28" s="148"/>
+      <c r="B28" s="63"/>
+      <c r="C28" s="149"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="149"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="156"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="156"/>
+      <c r="K28" s="63"/>
+      <c r="L28" s="153"/>
+      <c r="M28" s="62"/>
+      <c r="N28" s="63"/>
+      <c r="O28" s="153"/>
+      <c r="P28" s="62"/>
+      <c r="Q28" s="63"/>
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
       <c r="T28" s="33"/>
@@ -10408,23 +10906,23 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="135"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="136"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="136"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="143"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="143"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="140"/>
-      <c r="M29" s="49"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="140"/>
-      <c r="P29" s="49"/>
-      <c r="Q29" s="50"/>
+      <c r="A29" s="148"/>
+      <c r="B29" s="63"/>
+      <c r="C29" s="149"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="149"/>
+      <c r="F29" s="63"/>
+      <c r="G29" s="156"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="63"/>
+      <c r="J29" s="156"/>
+      <c r="K29" s="63"/>
+      <c r="L29" s="153"/>
+      <c r="M29" s="62"/>
+      <c r="N29" s="63"/>
+      <c r="O29" s="153"/>
+      <c r="P29" s="62"/>
+      <c r="Q29" s="63"/>
       <c r="R29" s="32"/>
       <c r="S29" s="32"/>
       <c r="T29" s="33"/>
@@ -10436,23 +10934,23 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="135"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="136"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="136"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="143"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="143"/>
-      <c r="K30" s="50"/>
-      <c r="L30" s="140"/>
-      <c r="M30" s="49"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="140"/>
-      <c r="P30" s="49"/>
-      <c r="Q30" s="50"/>
+      <c r="A30" s="148"/>
+      <c r="B30" s="63"/>
+      <c r="C30" s="149"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="149"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="156"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="156"/>
+      <c r="K30" s="63"/>
+      <c r="L30" s="153"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="63"/>
+      <c r="O30" s="153"/>
+      <c r="P30" s="62"/>
+      <c r="Q30" s="63"/>
       <c r="R30" s="32"/>
       <c r="S30" s="32"/>
       <c r="T30" s="33"/>
@@ -10464,23 +10962,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="137"/>
-      <c r="B31" s="138"/>
-      <c r="C31" s="139"/>
-      <c r="D31" s="138"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="138"/>
-      <c r="G31" s="147"/>
-      <c r="H31" s="133"/>
-      <c r="I31" s="138"/>
-      <c r="J31" s="147"/>
-      <c r="K31" s="138"/>
-      <c r="L31" s="141"/>
-      <c r="M31" s="133"/>
-      <c r="N31" s="138"/>
-      <c r="O31" s="141"/>
-      <c r="P31" s="133"/>
-      <c r="Q31" s="138"/>
+      <c r="A31" s="150"/>
+      <c r="B31" s="151"/>
+      <c r="C31" s="152"/>
+      <c r="D31" s="151"/>
+      <c r="E31" s="152"/>
+      <c r="F31" s="151"/>
+      <c r="G31" s="164"/>
+      <c r="H31" s="146"/>
+      <c r="I31" s="151"/>
+      <c r="J31" s="164"/>
+      <c r="K31" s="151"/>
+      <c r="L31" s="154"/>
+      <c r="M31" s="146"/>
+      <c r="N31" s="151"/>
+      <c r="O31" s="154"/>
+      <c r="P31" s="146"/>
+      <c r="Q31" s="151"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -11619,4 +12117,1377 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20100C0A-C86A-4465-B785-9157351E8AB1}">
+  <dimension ref="A1:S52"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.25" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" style="49" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="60" customWidth="1"/>
+    <col min="3" max="6" width="8.140625" style="49" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" style="60" customWidth="1"/>
+    <col min="8" max="13" width="8.140625" style="49" customWidth="1"/>
+    <col min="14" max="19" width="12.140625" style="49" customWidth="1"/>
+    <col min="20" max="16384" width="8" style="49"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A1" s="185" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="185"/>
+      <c r="C1" s="186" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="187"/>
+      <c r="E1" s="188"/>
+      <c r="F1" s="189" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="190"/>
+      <c r="H1" s="190"/>
+      <c r="I1" s="190"/>
+      <c r="J1" s="190"/>
+      <c r="K1" s="190"/>
+      <c r="L1" s="190"/>
+      <c r="M1" s="191"/>
+      <c r="N1" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="O1" s="189" t="s">
+        <v>56</v>
+      </c>
+      <c r="P1" s="191"/>
+      <c r="Q1" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="R1" s="189" t="s">
+        <v>112</v>
+      </c>
+      <c r="S1" s="191"/>
+    </row>
+    <row r="2" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A2" s="185"/>
+      <c r="B2" s="185"/>
+      <c r="C2" s="186" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="187"/>
+      <c r="E2" s="188"/>
+      <c r="F2" s="189" t="s">
+        <v>114</v>
+      </c>
+      <c r="G2" s="190"/>
+      <c r="H2" s="190"/>
+      <c r="I2" s="190"/>
+      <c r="J2" s="190"/>
+      <c r="K2" s="190"/>
+      <c r="L2" s="190"/>
+      <c r="M2" s="191"/>
+      <c r="N2" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="O2" s="192">
+        <v>45818</v>
+      </c>
+      <c r="P2" s="193"/>
+      <c r="Q2" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="R2" s="194" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="195"/>
+    </row>
+    <row r="3" spans="1:19" ht="11.25" customHeight="1">
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
+    </row>
+    <row r="4" spans="1:19" ht="15" customHeight="1">
+      <c r="A4" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="176" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="177"/>
+      <c r="E4" s="177"/>
+      <c r="F4" s="177"/>
+      <c r="G4" s="178"/>
+      <c r="H4" s="176" t="s">
+        <v>120</v>
+      </c>
+      <c r="I4" s="177"/>
+      <c r="J4" s="177"/>
+      <c r="K4" s="177"/>
+      <c r="L4" s="177"/>
+      <c r="M4" s="178"/>
+      <c r="N4" s="176" t="s">
+        <v>121</v>
+      </c>
+      <c r="O4" s="177"/>
+      <c r="P4" s="178"/>
+      <c r="Q4" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="R4" s="176" t="s">
+        <v>123</v>
+      </c>
+      <c r="S4" s="178"/>
+    </row>
+    <row r="5" spans="1:19" ht="30" customHeight="1">
+      <c r="A5" s="55">
+        <v>1</v>
+      </c>
+      <c r="B5" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="179" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" s="179"/>
+      <c r="E5" s="179"/>
+      <c r="F5" s="179"/>
+      <c r="G5" s="179"/>
+      <c r="H5" s="179" t="s">
+        <v>126</v>
+      </c>
+      <c r="I5" s="179"/>
+      <c r="J5" s="179"/>
+      <c r="K5" s="179"/>
+      <c r="L5" s="179"/>
+      <c r="M5" s="179"/>
+      <c r="N5" s="180" t="s">
+        <v>127</v>
+      </c>
+      <c r="O5" s="181"/>
+      <c r="P5" s="182"/>
+      <c r="Q5" s="57">
+        <v>45824</v>
+      </c>
+      <c r="R5" s="183"/>
+      <c r="S5" s="184"/>
+    </row>
+    <row r="6" spans="1:19" ht="30" customHeight="1">
+      <c r="A6" s="58"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="165"/>
+      <c r="D6" s="165"/>
+      <c r="E6" s="165"/>
+      <c r="F6" s="165"/>
+      <c r="G6" s="165"/>
+      <c r="H6" s="165"/>
+      <c r="I6" s="165"/>
+      <c r="J6" s="165"/>
+      <c r="K6" s="165"/>
+      <c r="L6" s="165"/>
+      <c r="M6" s="165"/>
+      <c r="N6" s="173"/>
+      <c r="O6" s="174"/>
+      <c r="P6" s="175"/>
+      <c r="Q6" s="59"/>
+      <c r="R6" s="172"/>
+      <c r="S6" s="172"/>
+    </row>
+    <row r="7" spans="1:19" ht="30" customHeight="1">
+      <c r="A7" s="58"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="165"/>
+      <c r="D7" s="165"/>
+      <c r="E7" s="165"/>
+      <c r="F7" s="165"/>
+      <c r="G7" s="165"/>
+      <c r="H7" s="165"/>
+      <c r="I7" s="165"/>
+      <c r="J7" s="165"/>
+      <c r="K7" s="165"/>
+      <c r="L7" s="165"/>
+      <c r="M7" s="165"/>
+      <c r="N7" s="169"/>
+      <c r="O7" s="170"/>
+      <c r="P7" s="171"/>
+      <c r="Q7" s="59"/>
+      <c r="R7" s="172"/>
+      <c r="S7" s="172"/>
+    </row>
+    <row r="8" spans="1:19" ht="30" customHeight="1">
+      <c r="A8" s="58"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="165"/>
+      <c r="D8" s="165"/>
+      <c r="E8" s="165"/>
+      <c r="F8" s="165"/>
+      <c r="G8" s="165"/>
+      <c r="H8" s="165"/>
+      <c r="I8" s="165"/>
+      <c r="J8" s="165"/>
+      <c r="K8" s="165"/>
+      <c r="L8" s="165"/>
+      <c r="M8" s="165"/>
+      <c r="N8" s="169"/>
+      <c r="O8" s="170"/>
+      <c r="P8" s="171"/>
+      <c r="Q8" s="59"/>
+      <c r="R8" s="172"/>
+      <c r="S8" s="172"/>
+    </row>
+    <row r="9" spans="1:19" ht="30" customHeight="1">
+      <c r="A9" s="58"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="165"/>
+      <c r="D9" s="165"/>
+      <c r="E9" s="165"/>
+      <c r="F9" s="165"/>
+      <c r="G9" s="165"/>
+      <c r="H9" s="165"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
+      <c r="L9" s="165"/>
+      <c r="M9" s="165"/>
+      <c r="N9" s="169"/>
+      <c r="O9" s="170"/>
+      <c r="P9" s="171"/>
+      <c r="Q9" s="58"/>
+      <c r="R9" s="172"/>
+      <c r="S9" s="172"/>
+    </row>
+    <row r="10" spans="1:19" ht="30" customHeight="1">
+      <c r="A10" s="58"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="165"/>
+      <c r="D10" s="165"/>
+      <c r="E10" s="165"/>
+      <c r="F10" s="165"/>
+      <c r="G10" s="165"/>
+      <c r="H10" s="166"/>
+      <c r="I10" s="167"/>
+      <c r="J10" s="167"/>
+      <c r="K10" s="167"/>
+      <c r="L10" s="167"/>
+      <c r="M10" s="168"/>
+      <c r="N10" s="169"/>
+      <c r="O10" s="170"/>
+      <c r="P10" s="171"/>
+      <c r="Q10" s="59"/>
+      <c r="R10" s="172"/>
+      <c r="S10" s="172"/>
+    </row>
+    <row r="11" spans="1:19" ht="30" customHeight="1">
+      <c r="A11" s="58"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="165"/>
+      <c r="D11" s="165"/>
+      <c r="E11" s="165"/>
+      <c r="F11" s="165"/>
+      <c r="G11" s="165"/>
+      <c r="H11" s="166"/>
+      <c r="I11" s="167"/>
+      <c r="J11" s="167"/>
+      <c r="K11" s="167"/>
+      <c r="L11" s="167"/>
+      <c r="M11" s="168"/>
+      <c r="N11" s="169"/>
+      <c r="O11" s="170"/>
+      <c r="P11" s="171"/>
+      <c r="Q11" s="58"/>
+      <c r="R11" s="172"/>
+      <c r="S11" s="172"/>
+    </row>
+    <row r="12" spans="1:19" ht="30" customHeight="1">
+      <c r="A12" s="58"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="165"/>
+      <c r="D12" s="165"/>
+      <c r="E12" s="165"/>
+      <c r="F12" s="165"/>
+      <c r="G12" s="165"/>
+      <c r="H12" s="166"/>
+      <c r="I12" s="167"/>
+      <c r="J12" s="167"/>
+      <c r="K12" s="167"/>
+      <c r="L12" s="167"/>
+      <c r="M12" s="168"/>
+      <c r="N12" s="169"/>
+      <c r="O12" s="170"/>
+      <c r="P12" s="171"/>
+      <c r="Q12" s="58"/>
+      <c r="R12" s="172"/>
+      <c r="S12" s="172"/>
+    </row>
+    <row r="13" spans="1:19" ht="30" customHeight="1">
+      <c r="A13" s="58"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="165"/>
+      <c r="D13" s="165"/>
+      <c r="E13" s="165"/>
+      <c r="F13" s="165"/>
+      <c r="G13" s="165"/>
+      <c r="H13" s="166"/>
+      <c r="I13" s="167"/>
+      <c r="J13" s="167"/>
+      <c r="K13" s="167"/>
+      <c r="L13" s="167"/>
+      <c r="M13" s="168"/>
+      <c r="N13" s="169"/>
+      <c r="O13" s="170"/>
+      <c r="P13" s="171"/>
+      <c r="Q13" s="58"/>
+      <c r="R13" s="172"/>
+      <c r="S13" s="172"/>
+    </row>
+    <row r="14" spans="1:19" ht="30" customHeight="1">
+      <c r="A14" s="58"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="165"/>
+      <c r="D14" s="165"/>
+      <c r="E14" s="165"/>
+      <c r="F14" s="165"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="166"/>
+      <c r="I14" s="167"/>
+      <c r="J14" s="167"/>
+      <c r="K14" s="167"/>
+      <c r="L14" s="167"/>
+      <c r="M14" s="168"/>
+      <c r="N14" s="169"/>
+      <c r="O14" s="170"/>
+      <c r="P14" s="171"/>
+      <c r="Q14" s="58"/>
+      <c r="R14" s="172"/>
+      <c r="S14" s="172"/>
+    </row>
+    <row r="15" spans="1:19" ht="30" customHeight="1">
+      <c r="A15" s="58"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="165"/>
+      <c r="D15" s="165"/>
+      <c r="E15" s="165"/>
+      <c r="F15" s="165"/>
+      <c r="G15" s="165"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="167"/>
+      <c r="J15" s="167"/>
+      <c r="K15" s="167"/>
+      <c r="L15" s="167"/>
+      <c r="M15" s="168"/>
+      <c r="N15" s="169"/>
+      <c r="O15" s="170"/>
+      <c r="P15" s="171"/>
+      <c r="Q15" s="58"/>
+      <c r="R15" s="172"/>
+      <c r="S15" s="172"/>
+    </row>
+    <row r="16" spans="1:19" ht="30" customHeight="1">
+      <c r="A16" s="58"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="165"/>
+      <c r="D16" s="165"/>
+      <c r="E16" s="165"/>
+      <c r="F16" s="165"/>
+      <c r="G16" s="165"/>
+      <c r="H16" s="166"/>
+      <c r="I16" s="167"/>
+      <c r="J16" s="167"/>
+      <c r="K16" s="167"/>
+      <c r="L16" s="167"/>
+      <c r="M16" s="168"/>
+      <c r="N16" s="169"/>
+      <c r="O16" s="170"/>
+      <c r="P16" s="171"/>
+      <c r="Q16" s="58"/>
+      <c r="R16" s="172"/>
+      <c r="S16" s="172"/>
+    </row>
+    <row r="17" spans="1:19" ht="30" customHeight="1">
+      <c r="A17" s="58"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="165"/>
+      <c r="D17" s="165"/>
+      <c r="E17" s="165"/>
+      <c r="F17" s="165"/>
+      <c r="G17" s="165"/>
+      <c r="H17" s="166"/>
+      <c r="I17" s="167"/>
+      <c r="J17" s="167"/>
+      <c r="K17" s="167"/>
+      <c r="L17" s="167"/>
+      <c r="M17" s="168"/>
+      <c r="N17" s="169"/>
+      <c r="O17" s="170"/>
+      <c r="P17" s="171"/>
+      <c r="Q17" s="58"/>
+      <c r="R17" s="172"/>
+      <c r="S17" s="172"/>
+    </row>
+    <row r="18" spans="1:19" ht="30" customHeight="1">
+      <c r="A18" s="58"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="165"/>
+      <c r="D18" s="165"/>
+      <c r="E18" s="165"/>
+      <c r="F18" s="165"/>
+      <c r="G18" s="165"/>
+      <c r="H18" s="166"/>
+      <c r="I18" s="167"/>
+      <c r="J18" s="167"/>
+      <c r="K18" s="167"/>
+      <c r="L18" s="167"/>
+      <c r="M18" s="168"/>
+      <c r="N18" s="169"/>
+      <c r="O18" s="170"/>
+      <c r="P18" s="171"/>
+      <c r="Q18" s="58"/>
+      <c r="R18" s="172"/>
+      <c r="S18" s="172"/>
+    </row>
+    <row r="19" spans="1:19" ht="30" customHeight="1">
+      <c r="A19" s="58"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="165"/>
+      <c r="D19" s="165"/>
+      <c r="E19" s="165"/>
+      <c r="F19" s="165"/>
+      <c r="G19" s="165"/>
+      <c r="H19" s="166"/>
+      <c r="I19" s="167"/>
+      <c r="J19" s="167"/>
+      <c r="K19" s="167"/>
+      <c r="L19" s="167"/>
+      <c r="M19" s="168"/>
+      <c r="N19" s="169"/>
+      <c r="O19" s="170"/>
+      <c r="P19" s="171"/>
+      <c r="Q19" s="58"/>
+      <c r="R19" s="172"/>
+      <c r="S19" s="172"/>
+    </row>
+    <row r="20" spans="1:19" ht="30" customHeight="1">
+      <c r="A20" s="58"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="165"/>
+      <c r="D20" s="165"/>
+      <c r="E20" s="165"/>
+      <c r="F20" s="165"/>
+      <c r="G20" s="165"/>
+      <c r="H20" s="166"/>
+      <c r="I20" s="167"/>
+      <c r="J20" s="167"/>
+      <c r="K20" s="167"/>
+      <c r="L20" s="167"/>
+      <c r="M20" s="168"/>
+      <c r="N20" s="169"/>
+      <c r="O20" s="170"/>
+      <c r="P20" s="171"/>
+      <c r="Q20" s="58"/>
+      <c r="R20" s="172"/>
+      <c r="S20" s="172"/>
+    </row>
+    <row r="21" spans="1:19" ht="30" customHeight="1">
+      <c r="A21" s="58"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="165"/>
+      <c r="D21" s="165"/>
+      <c r="E21" s="165"/>
+      <c r="F21" s="165"/>
+      <c r="G21" s="165"/>
+      <c r="H21" s="166"/>
+      <c r="I21" s="167"/>
+      <c r="J21" s="167"/>
+      <c r="K21" s="167"/>
+      <c r="L21" s="167"/>
+      <c r="M21" s="168"/>
+      <c r="N21" s="169"/>
+      <c r="O21" s="170"/>
+      <c r="P21" s="171"/>
+      <c r="Q21" s="58"/>
+      <c r="R21" s="172"/>
+      <c r="S21" s="172"/>
+    </row>
+    <row r="22" spans="1:19" ht="30" customHeight="1">
+      <c r="A22" s="58"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="165"/>
+      <c r="D22" s="165"/>
+      <c r="E22" s="165"/>
+      <c r="F22" s="165"/>
+      <c r="G22" s="165"/>
+      <c r="H22" s="166"/>
+      <c r="I22" s="167"/>
+      <c r="J22" s="167"/>
+      <c r="K22" s="167"/>
+      <c r="L22" s="167"/>
+      <c r="M22" s="168"/>
+      <c r="N22" s="169"/>
+      <c r="O22" s="170"/>
+      <c r="P22" s="171"/>
+      <c r="Q22" s="58"/>
+      <c r="R22" s="172"/>
+      <c r="S22" s="172"/>
+    </row>
+    <row r="23" spans="1:19" ht="30" customHeight="1">
+      <c r="A23" s="58"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="165"/>
+      <c r="D23" s="165"/>
+      <c r="E23" s="165"/>
+      <c r="F23" s="165"/>
+      <c r="G23" s="165"/>
+      <c r="H23" s="166"/>
+      <c r="I23" s="167"/>
+      <c r="J23" s="167"/>
+      <c r="K23" s="167"/>
+      <c r="L23" s="167"/>
+      <c r="M23" s="168"/>
+      <c r="N23" s="169"/>
+      <c r="O23" s="170"/>
+      <c r="P23" s="171"/>
+      <c r="Q23" s="58"/>
+      <c r="R23" s="172"/>
+      <c r="S23" s="172"/>
+    </row>
+    <row r="24" spans="1:19" ht="30" customHeight="1">
+      <c r="A24" s="58"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="165"/>
+      <c r="D24" s="165"/>
+      <c r="E24" s="165"/>
+      <c r="F24" s="165"/>
+      <c r="G24" s="165"/>
+      <c r="H24" s="166"/>
+      <c r="I24" s="167"/>
+      <c r="J24" s="167"/>
+      <c r="K24" s="167"/>
+      <c r="L24" s="167"/>
+      <c r="M24" s="168"/>
+      <c r="N24" s="169"/>
+      <c r="O24" s="170"/>
+      <c r="P24" s="171"/>
+      <c r="Q24" s="58"/>
+      <c r="R24" s="172"/>
+      <c r="S24" s="172"/>
+    </row>
+    <row r="25" spans="1:19" ht="30" customHeight="1">
+      <c r="A25" s="58"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="165"/>
+      <c r="D25" s="165"/>
+      <c r="E25" s="165"/>
+      <c r="F25" s="165"/>
+      <c r="G25" s="165"/>
+      <c r="H25" s="166"/>
+      <c r="I25" s="167"/>
+      <c r="J25" s="167"/>
+      <c r="K25" s="167"/>
+      <c r="L25" s="167"/>
+      <c r="M25" s="168"/>
+      <c r="N25" s="169"/>
+      <c r="O25" s="170"/>
+      <c r="P25" s="171"/>
+      <c r="Q25" s="58"/>
+      <c r="R25" s="172"/>
+      <c r="S25" s="172"/>
+    </row>
+    <row r="26" spans="1:19" ht="30" customHeight="1">
+      <c r="A26" s="58"/>
+      <c r="B26" s="58"/>
+      <c r="C26" s="165"/>
+      <c r="D26" s="165"/>
+      <c r="E26" s="165"/>
+      <c r="F26" s="165"/>
+      <c r="G26" s="165"/>
+      <c r="H26" s="166"/>
+      <c r="I26" s="167"/>
+      <c r="J26" s="167"/>
+      <c r="K26" s="167"/>
+      <c r="L26" s="167"/>
+      <c r="M26" s="168"/>
+      <c r="N26" s="169"/>
+      <c r="O26" s="170"/>
+      <c r="P26" s="171"/>
+      <c r="Q26" s="58"/>
+      <c r="R26" s="172"/>
+      <c r="S26" s="172"/>
+    </row>
+    <row r="27" spans="1:19" ht="30" customHeight="1">
+      <c r="A27" s="58"/>
+      <c r="B27" s="58"/>
+      <c r="C27" s="165"/>
+      <c r="D27" s="165"/>
+      <c r="E27" s="165"/>
+      <c r="F27" s="165"/>
+      <c r="G27" s="165"/>
+      <c r="H27" s="166"/>
+      <c r="I27" s="167"/>
+      <c r="J27" s="167"/>
+      <c r="K27" s="167"/>
+      <c r="L27" s="167"/>
+      <c r="M27" s="168"/>
+      <c r="N27" s="169"/>
+      <c r="O27" s="170"/>
+      <c r="P27" s="171"/>
+      <c r="Q27" s="58"/>
+      <c r="R27" s="172"/>
+      <c r="S27" s="172"/>
+    </row>
+    <row r="28" spans="1:19" ht="30" customHeight="1">
+      <c r="A28" s="58"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="165"/>
+      <c r="D28" s="165"/>
+      <c r="E28" s="165"/>
+      <c r="F28" s="165"/>
+      <c r="G28" s="165"/>
+      <c r="H28" s="166"/>
+      <c r="I28" s="167"/>
+      <c r="J28" s="167"/>
+      <c r="K28" s="167"/>
+      <c r="L28" s="167"/>
+      <c r="M28" s="168"/>
+      <c r="N28" s="169"/>
+      <c r="O28" s="170"/>
+      <c r="P28" s="171"/>
+      <c r="Q28" s="58"/>
+      <c r="R28" s="172"/>
+      <c r="S28" s="172"/>
+    </row>
+    <row r="29" spans="1:19" ht="30" customHeight="1">
+      <c r="A29" s="58"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="165"/>
+      <c r="D29" s="165"/>
+      <c r="E29" s="165"/>
+      <c r="F29" s="165"/>
+      <c r="G29" s="165"/>
+      <c r="H29" s="166"/>
+      <c r="I29" s="167"/>
+      <c r="J29" s="167"/>
+      <c r="K29" s="167"/>
+      <c r="L29" s="167"/>
+      <c r="M29" s="168"/>
+      <c r="N29" s="169"/>
+      <c r="O29" s="170"/>
+      <c r="P29" s="171"/>
+      <c r="Q29" s="58"/>
+      <c r="R29" s="172"/>
+      <c r="S29" s="172"/>
+    </row>
+    <row r="30" spans="1:19" ht="30" customHeight="1">
+      <c r="A30" s="58"/>
+      <c r="B30" s="58"/>
+      <c r="C30" s="165"/>
+      <c r="D30" s="165"/>
+      <c r="E30" s="165"/>
+      <c r="F30" s="165"/>
+      <c r="G30" s="165"/>
+      <c r="H30" s="166"/>
+      <c r="I30" s="167"/>
+      <c r="J30" s="167"/>
+      <c r="K30" s="167"/>
+      <c r="L30" s="167"/>
+      <c r="M30" s="168"/>
+      <c r="N30" s="169"/>
+      <c r="O30" s="170"/>
+      <c r="P30" s="171"/>
+      <c r="Q30" s="58"/>
+      <c r="R30" s="172"/>
+      <c r="S30" s="172"/>
+    </row>
+    <row r="31" spans="1:19" ht="30" customHeight="1">
+      <c r="A31" s="58"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="165"/>
+      <c r="D31" s="165"/>
+      <c r="E31" s="165"/>
+      <c r="F31" s="165"/>
+      <c r="G31" s="165"/>
+      <c r="H31" s="166"/>
+      <c r="I31" s="167"/>
+      <c r="J31" s="167"/>
+      <c r="K31" s="167"/>
+      <c r="L31" s="167"/>
+      <c r="M31" s="168"/>
+      <c r="N31" s="169"/>
+      <c r="O31" s="170"/>
+      <c r="P31" s="171"/>
+      <c r="Q31" s="58"/>
+      <c r="R31" s="172"/>
+      <c r="S31" s="172"/>
+    </row>
+    <row r="32" spans="1:19" ht="30" customHeight="1">
+      <c r="A32" s="58"/>
+      <c r="B32" s="58"/>
+      <c r="C32" s="165"/>
+      <c r="D32" s="165"/>
+      <c r="E32" s="165"/>
+      <c r="F32" s="165"/>
+      <c r="G32" s="165"/>
+      <c r="H32" s="166"/>
+      <c r="I32" s="167"/>
+      <c r="J32" s="167"/>
+      <c r="K32" s="167"/>
+      <c r="L32" s="167"/>
+      <c r="M32" s="168"/>
+      <c r="N32" s="169"/>
+      <c r="O32" s="170"/>
+      <c r="P32" s="171"/>
+      <c r="Q32" s="58"/>
+      <c r="R32" s="172"/>
+      <c r="S32" s="172"/>
+    </row>
+    <row r="33" spans="1:19" ht="30" customHeight="1">
+      <c r="A33" s="58"/>
+      <c r="B33" s="58"/>
+      <c r="C33" s="165"/>
+      <c r="D33" s="165"/>
+      <c r="E33" s="165"/>
+      <c r="F33" s="165"/>
+      <c r="G33" s="165"/>
+      <c r="H33" s="166"/>
+      <c r="I33" s="167"/>
+      <c r="J33" s="167"/>
+      <c r="K33" s="167"/>
+      <c r="L33" s="167"/>
+      <c r="M33" s="168"/>
+      <c r="N33" s="169"/>
+      <c r="O33" s="170"/>
+      <c r="P33" s="171"/>
+      <c r="Q33" s="58"/>
+      <c r="R33" s="172"/>
+      <c r="S33" s="172"/>
+    </row>
+    <row r="34" spans="1:19" ht="30" customHeight="1">
+      <c r="A34" s="58"/>
+      <c r="B34" s="58"/>
+      <c r="C34" s="165"/>
+      <c r="D34" s="165"/>
+      <c r="E34" s="165"/>
+      <c r="F34" s="165"/>
+      <c r="G34" s="165"/>
+      <c r="H34" s="166"/>
+      <c r="I34" s="167"/>
+      <c r="J34" s="167"/>
+      <c r="K34" s="167"/>
+      <c r="L34" s="167"/>
+      <c r="M34" s="168"/>
+      <c r="N34" s="169"/>
+      <c r="O34" s="170"/>
+      <c r="P34" s="171"/>
+      <c r="Q34" s="58"/>
+      <c r="R34" s="172"/>
+      <c r="S34" s="172"/>
+    </row>
+    <row r="35" spans="1:19" ht="30" customHeight="1">
+      <c r="A35" s="58"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="165"/>
+      <c r="D35" s="165"/>
+      <c r="E35" s="165"/>
+      <c r="F35" s="165"/>
+      <c r="G35" s="165"/>
+      <c r="H35" s="166"/>
+      <c r="I35" s="167"/>
+      <c r="J35" s="167"/>
+      <c r="K35" s="167"/>
+      <c r="L35" s="167"/>
+      <c r="M35" s="168"/>
+      <c r="N35" s="169"/>
+      <c r="O35" s="170"/>
+      <c r="P35" s="171"/>
+      <c r="Q35" s="58"/>
+      <c r="R35" s="172"/>
+      <c r="S35" s="172"/>
+    </row>
+    <row r="36" spans="1:19" ht="30" customHeight="1">
+      <c r="A36" s="58"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="165"/>
+      <c r="D36" s="165"/>
+      <c r="E36" s="165"/>
+      <c r="F36" s="165"/>
+      <c r="G36" s="165"/>
+      <c r="H36" s="166"/>
+      <c r="I36" s="167"/>
+      <c r="J36" s="167"/>
+      <c r="K36" s="167"/>
+      <c r="L36" s="167"/>
+      <c r="M36" s="168"/>
+      <c r="N36" s="169"/>
+      <c r="O36" s="170"/>
+      <c r="P36" s="171"/>
+      <c r="Q36" s="58"/>
+      <c r="R36" s="172"/>
+      <c r="S36" s="172"/>
+    </row>
+    <row r="37" spans="1:19" ht="30" customHeight="1">
+      <c r="A37" s="58"/>
+      <c r="B37" s="58"/>
+      <c r="C37" s="165"/>
+      <c r="D37" s="165"/>
+      <c r="E37" s="165"/>
+      <c r="F37" s="165"/>
+      <c r="G37" s="165"/>
+      <c r="H37" s="166"/>
+      <c r="I37" s="167"/>
+      <c r="J37" s="167"/>
+      <c r="K37" s="167"/>
+      <c r="L37" s="167"/>
+      <c r="M37" s="168"/>
+      <c r="N37" s="169"/>
+      <c r="O37" s="170"/>
+      <c r="P37" s="171"/>
+      <c r="Q37" s="58"/>
+      <c r="R37" s="172"/>
+      <c r="S37" s="172"/>
+    </row>
+    <row r="38" spans="1:19" ht="30" customHeight="1">
+      <c r="A38" s="58"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="165"/>
+      <c r="D38" s="165"/>
+      <c r="E38" s="165"/>
+      <c r="F38" s="165"/>
+      <c r="G38" s="165"/>
+      <c r="H38" s="166"/>
+      <c r="I38" s="167"/>
+      <c r="J38" s="167"/>
+      <c r="K38" s="167"/>
+      <c r="L38" s="167"/>
+      <c r="M38" s="168"/>
+      <c r="N38" s="169"/>
+      <c r="O38" s="170"/>
+      <c r="P38" s="171"/>
+      <c r="Q38" s="58"/>
+      <c r="R38" s="172"/>
+      <c r="S38" s="172"/>
+    </row>
+    <row r="39" spans="1:19" ht="30" customHeight="1">
+      <c r="A39" s="58"/>
+      <c r="B39" s="58"/>
+      <c r="C39" s="165"/>
+      <c r="D39" s="165"/>
+      <c r="E39" s="165"/>
+      <c r="F39" s="165"/>
+      <c r="G39" s="165"/>
+      <c r="H39" s="166"/>
+      <c r="I39" s="167"/>
+      <c r="J39" s="167"/>
+      <c r="K39" s="167"/>
+      <c r="L39" s="167"/>
+      <c r="M39" s="168"/>
+      <c r="N39" s="169"/>
+      <c r="O39" s="170"/>
+      <c r="P39" s="171"/>
+      <c r="Q39" s="58"/>
+      <c r="R39" s="172"/>
+      <c r="S39" s="172"/>
+    </row>
+    <row r="40" spans="1:19" ht="30" customHeight="1">
+      <c r="A40" s="58"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="165"/>
+      <c r="D40" s="165"/>
+      <c r="E40" s="165"/>
+      <c r="F40" s="165"/>
+      <c r="G40" s="165"/>
+      <c r="H40" s="166"/>
+      <c r="I40" s="167"/>
+      <c r="J40" s="167"/>
+      <c r="K40" s="167"/>
+      <c r="L40" s="167"/>
+      <c r="M40" s="168"/>
+      <c r="N40" s="169"/>
+      <c r="O40" s="170"/>
+      <c r="P40" s="171"/>
+      <c r="Q40" s="58"/>
+      <c r="R40" s="172"/>
+      <c r="S40" s="172"/>
+    </row>
+    <row r="41" spans="1:19" ht="30" customHeight="1">
+      <c r="A41" s="58"/>
+      <c r="B41" s="58"/>
+      <c r="C41" s="165"/>
+      <c r="D41" s="165"/>
+      <c r="E41" s="165"/>
+      <c r="F41" s="165"/>
+      <c r="G41" s="165"/>
+      <c r="H41" s="166"/>
+      <c r="I41" s="167"/>
+      <c r="J41" s="167"/>
+      <c r="K41" s="167"/>
+      <c r="L41" s="167"/>
+      <c r="M41" s="168"/>
+      <c r="N41" s="169"/>
+      <c r="O41" s="170"/>
+      <c r="P41" s="171"/>
+      <c r="Q41" s="58"/>
+      <c r="R41" s="172"/>
+      <c r="S41" s="172"/>
+    </row>
+    <row r="42" spans="1:19" ht="30" customHeight="1">
+      <c r="A42" s="58"/>
+      <c r="B42" s="58"/>
+      <c r="C42" s="165"/>
+      <c r="D42" s="165"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="165"/>
+      <c r="H42" s="166"/>
+      <c r="I42" s="167"/>
+      <c r="J42" s="167"/>
+      <c r="K42" s="167"/>
+      <c r="L42" s="167"/>
+      <c r="M42" s="168"/>
+      <c r="N42" s="169"/>
+      <c r="O42" s="170"/>
+      <c r="P42" s="171"/>
+      <c r="Q42" s="58"/>
+      <c r="R42" s="172"/>
+      <c r="S42" s="172"/>
+    </row>
+    <row r="43" spans="1:19" ht="30" customHeight="1">
+      <c r="A43" s="58"/>
+      <c r="B43" s="58"/>
+      <c r="C43" s="165"/>
+      <c r="D43" s="165"/>
+      <c r="E43" s="165"/>
+      <c r="F43" s="165"/>
+      <c r="G43" s="165"/>
+      <c r="H43" s="166"/>
+      <c r="I43" s="167"/>
+      <c r="J43" s="167"/>
+      <c r="K43" s="167"/>
+      <c r="L43" s="167"/>
+      <c r="M43" s="168"/>
+      <c r="N43" s="169"/>
+      <c r="O43" s="170"/>
+      <c r="P43" s="171"/>
+      <c r="Q43" s="58"/>
+      <c r="R43" s="172"/>
+      <c r="S43" s="172"/>
+    </row>
+    <row r="44" spans="1:19" ht="30" customHeight="1">
+      <c r="A44" s="58"/>
+      <c r="B44" s="58"/>
+      <c r="C44" s="165"/>
+      <c r="D44" s="165"/>
+      <c r="E44" s="165"/>
+      <c r="F44" s="165"/>
+      <c r="G44" s="165"/>
+      <c r="H44" s="166"/>
+      <c r="I44" s="167"/>
+      <c r="J44" s="167"/>
+      <c r="K44" s="167"/>
+      <c r="L44" s="167"/>
+      <c r="M44" s="168"/>
+      <c r="N44" s="169"/>
+      <c r="O44" s="170"/>
+      <c r="P44" s="171"/>
+      <c r="Q44" s="58"/>
+      <c r="R44" s="172"/>
+      <c r="S44" s="172"/>
+    </row>
+    <row r="45" spans="1:19" ht="30" customHeight="1">
+      <c r="A45" s="58"/>
+      <c r="B45" s="58"/>
+      <c r="C45" s="165"/>
+      <c r="D45" s="165"/>
+      <c r="E45" s="165"/>
+      <c r="F45" s="165"/>
+      <c r="G45" s="165"/>
+      <c r="H45" s="166"/>
+      <c r="I45" s="167"/>
+      <c r="J45" s="167"/>
+      <c r="K45" s="167"/>
+      <c r="L45" s="167"/>
+      <c r="M45" s="168"/>
+      <c r="N45" s="169"/>
+      <c r="O45" s="170"/>
+      <c r="P45" s="171"/>
+      <c r="Q45" s="58"/>
+      <c r="R45" s="172"/>
+      <c r="S45" s="172"/>
+    </row>
+    <row r="46" spans="1:19" ht="30" customHeight="1">
+      <c r="A46" s="58"/>
+      <c r="B46" s="58"/>
+      <c r="C46" s="165"/>
+      <c r="D46" s="165"/>
+      <c r="E46" s="165"/>
+      <c r="F46" s="165"/>
+      <c r="G46" s="165"/>
+      <c r="H46" s="166"/>
+      <c r="I46" s="167"/>
+      <c r="J46" s="167"/>
+      <c r="K46" s="167"/>
+      <c r="L46" s="167"/>
+      <c r="M46" s="168"/>
+      <c r="N46" s="169"/>
+      <c r="O46" s="170"/>
+      <c r="P46" s="171"/>
+      <c r="Q46" s="58"/>
+      <c r="R46" s="172"/>
+      <c r="S46" s="172"/>
+    </row>
+    <row r="47" spans="1:19" ht="30" customHeight="1">
+      <c r="A47" s="58"/>
+      <c r="B47" s="58"/>
+      <c r="C47" s="165"/>
+      <c r="D47" s="165"/>
+      <c r="E47" s="165"/>
+      <c r="F47" s="165"/>
+      <c r="G47" s="165"/>
+      <c r="H47" s="166"/>
+      <c r="I47" s="167"/>
+      <c r="J47" s="167"/>
+      <c r="K47" s="167"/>
+      <c r="L47" s="167"/>
+      <c r="M47" s="168"/>
+      <c r="N47" s="169"/>
+      <c r="O47" s="170"/>
+      <c r="P47" s="171"/>
+      <c r="Q47" s="58"/>
+      <c r="R47" s="172"/>
+      <c r="S47" s="172"/>
+    </row>
+    <row r="48" spans="1:19" ht="30" customHeight="1">
+      <c r="A48" s="58"/>
+      <c r="B48" s="58"/>
+      <c r="C48" s="165"/>
+      <c r="D48" s="165"/>
+      <c r="E48" s="165"/>
+      <c r="F48" s="165"/>
+      <c r="G48" s="165"/>
+      <c r="H48" s="166"/>
+      <c r="I48" s="167"/>
+      <c r="J48" s="167"/>
+      <c r="K48" s="167"/>
+      <c r="L48" s="167"/>
+      <c r="M48" s="168"/>
+      <c r="N48" s="169"/>
+      <c r="O48" s="170"/>
+      <c r="P48" s="171"/>
+      <c r="Q48" s="58"/>
+      <c r="R48" s="172"/>
+      <c r="S48" s="172"/>
+    </row>
+    <row r="49" spans="1:19" ht="30" customHeight="1">
+      <c r="A49" s="58"/>
+      <c r="B49" s="58"/>
+      <c r="C49" s="165"/>
+      <c r="D49" s="165"/>
+      <c r="E49" s="165"/>
+      <c r="F49" s="165"/>
+      <c r="G49" s="165"/>
+      <c r="H49" s="166"/>
+      <c r="I49" s="167"/>
+      <c r="J49" s="167"/>
+      <c r="K49" s="167"/>
+      <c r="L49" s="167"/>
+      <c r="M49" s="168"/>
+      <c r="N49" s="169"/>
+      <c r="O49" s="170"/>
+      <c r="P49" s="171"/>
+      <c r="Q49" s="58"/>
+      <c r="R49" s="172"/>
+      <c r="S49" s="172"/>
+    </row>
+    <row r="50" spans="1:19" ht="30" customHeight="1">
+      <c r="A50" s="58"/>
+      <c r="B50" s="58"/>
+      <c r="C50" s="165"/>
+      <c r="D50" s="165"/>
+      <c r="E50" s="165"/>
+      <c r="F50" s="165"/>
+      <c r="G50" s="165"/>
+      <c r="H50" s="166"/>
+      <c r="I50" s="167"/>
+      <c r="J50" s="167"/>
+      <c r="K50" s="167"/>
+      <c r="L50" s="167"/>
+      <c r="M50" s="168"/>
+      <c r="N50" s="169"/>
+      <c r="O50" s="170"/>
+      <c r="P50" s="171"/>
+      <c r="Q50" s="58"/>
+      <c r="R50" s="172"/>
+      <c r="S50" s="172"/>
+    </row>
+    <row r="51" spans="1:19" ht="30" customHeight="1">
+      <c r="A51" s="58"/>
+      <c r="B51" s="58"/>
+      <c r="C51" s="165"/>
+      <c r="D51" s="165"/>
+      <c r="E51" s="165"/>
+      <c r="F51" s="165"/>
+      <c r="G51" s="165"/>
+      <c r="H51" s="166"/>
+      <c r="I51" s="167"/>
+      <c r="J51" s="167"/>
+      <c r="K51" s="167"/>
+      <c r="L51" s="167"/>
+      <c r="M51" s="168"/>
+      <c r="N51" s="169"/>
+      <c r="O51" s="170"/>
+      <c r="P51" s="171"/>
+      <c r="Q51" s="58"/>
+      <c r="R51" s="172"/>
+      <c r="S51" s="172"/>
+    </row>
+    <row r="52" spans="1:19" ht="30" customHeight="1">
+      <c r="A52" s="58"/>
+      <c r="B52" s="58"/>
+      <c r="C52" s="165"/>
+      <c r="D52" s="165"/>
+      <c r="E52" s="165"/>
+      <c r="F52" s="165"/>
+      <c r="G52" s="165"/>
+      <c r="H52" s="166"/>
+      <c r="I52" s="167"/>
+      <c r="J52" s="167"/>
+      <c r="K52" s="167"/>
+      <c r="L52" s="167"/>
+      <c r="M52" s="168"/>
+      <c r="N52" s="169"/>
+      <c r="O52" s="170"/>
+      <c r="P52" s="171"/>
+      <c r="Q52" s="58"/>
+      <c r="R52" s="172"/>
+      <c r="S52" s="172"/>
+    </row>
+  </sheetData>
+  <mergeCells count="205">
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="H5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
 </file>